--- a/Production/PiGarage-all-pos.xlsx
+++ b/Production/PiGarage-all-pos.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Bryce\Desktop\pwr_mgmt\Production\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{694FCB1F-909A-4C92-96D5-C38E60D4559A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D06E3CFE-F9E9-46D0-8D66-B0EA7BFB6D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{A6D97A3C-9F31-44A3-A97E-C04D722AD086}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{3F831818-1336-47B6-9A3D-B13D4A71934A}"/>
   </bookViews>
   <sheets>
     <sheet name="PiGarage-all-pos" sheetId="1" r:id="rId1"/>
@@ -20,68 +20,80 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="145">
   <si>
     <t>Package</t>
   </si>
   <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>Conn_02x20_Odd_Even</t>
+  </si>
+  <si>
+    <t>PinSocket_2x20_P2.54mm_Vertical</t>
+  </si>
+  <si>
+    <t>bottom</t>
+  </si>
+  <si>
     <t>C1</t>
   </si>
   <si>
+    <t>4.7ÂµF</t>
+  </si>
+  <si>
+    <t>C_1206_3216Metric</t>
+  </si>
+  <si>
+    <t>top</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>100nF</t>
+  </si>
+  <si>
+    <t>C_0603_1608Metric</t>
+  </si>
+  <si>
+    <t>C3</t>
+  </si>
+  <si>
+    <t>1.8nF</t>
+  </si>
+  <si>
+    <t>C4</t>
+  </si>
+  <si>
+    <t>8.2pF</t>
+  </si>
+  <si>
+    <t>C5</t>
+  </si>
+  <si>
+    <t>47ÂµF</t>
+  </si>
+  <si>
+    <t>C6</t>
+  </si>
+  <si>
+    <t>C7</t>
+  </si>
+  <si>
+    <t>C8</t>
+  </si>
+  <si>
     <t>10ÂµF</t>
   </si>
   <si>
-    <t>C_0805_2012Metric</t>
-  </si>
-  <si>
-    <t>top</t>
-  </si>
-  <si>
-    <t>C2</t>
-  </si>
-  <si>
-    <t>100nF</t>
-  </si>
-  <si>
-    <t>C_0402_1005Metric</t>
-  </si>
-  <si>
-    <t>C3</t>
+    <t>C9</t>
   </si>
   <si>
     <t>1ÂµF</t>
   </si>
   <si>
-    <t>C4</t>
-  </si>
-  <si>
-    <t>47ÂµF</t>
-  </si>
-  <si>
-    <t>CP_Elec_6.3x5.7</t>
-  </si>
-  <si>
-    <t>C5</t>
-  </si>
-  <si>
-    <t>47pF</t>
-  </si>
-  <si>
-    <t>C6</t>
-  </si>
-  <si>
-    <t>1nF</t>
-  </si>
-  <si>
-    <t>C7</t>
-  </si>
-  <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>C9</t>
-  </si>
-  <si>
     <t>C10</t>
   </si>
   <si>
@@ -94,9 +106,15 @@
     <t>C13</t>
   </si>
   <si>
+    <t>0.1ÂµF</t>
+  </si>
+  <si>
     <t>C14</t>
   </si>
   <si>
+    <t>2.2ÂµF</t>
+  </si>
+  <si>
     <t>C15</t>
   </si>
   <si>
@@ -109,60 +127,81 @@
     <t>C18</t>
   </si>
   <si>
+    <t>C19</t>
+  </si>
+  <si>
+    <t>C20</t>
+  </si>
+  <si>
+    <t>C21</t>
+  </si>
+  <si>
+    <t>C22</t>
+  </si>
+  <si>
+    <t>C23</t>
+  </si>
+  <si>
     <t>2.2nF</t>
   </si>
   <si>
-    <t>C_0603_1608Metric</t>
-  </si>
-  <si>
-    <t>C19</t>
-  </si>
-  <si>
-    <t>C20</t>
-  </si>
-  <si>
-    <t>C21</t>
-  </si>
-  <si>
-    <t>C22</t>
-  </si>
-  <si>
-    <t>C23</t>
-  </si>
-  <si>
     <t>C24</t>
   </si>
   <si>
     <t>C25</t>
   </si>
   <si>
+    <t>C26</t>
+  </si>
+  <si>
+    <t>C27</t>
+  </si>
+  <si>
+    <t>C28</t>
+  </si>
+  <si>
+    <t>C29</t>
+  </si>
+  <si>
+    <t>C30</t>
+  </si>
+  <si>
+    <t>C31</t>
+  </si>
+  <si>
+    <t>C32</t>
+  </si>
+  <si>
+    <t>C33</t>
+  </si>
+  <si>
     <t>D1</t>
   </si>
   <si>
-    <t>D_TVS</t>
-  </si>
-  <si>
-    <t>D_SMB</t>
+    <t>SMBJ18CA</t>
+  </si>
+  <si>
+    <t>D_SMC</t>
   </si>
   <si>
     <t>D2</t>
   </si>
   <si>
-    <t>D_Schottky_Dual_CommonCathode_AKA</t>
+    <t>B560C-13-F</t>
+  </si>
+  <si>
+    <t>SMC_L7.1-W6.2-LS8.1-RD</t>
+  </si>
+  <si>
+    <t>D3</t>
+  </si>
+  <si>
+    <t>BAT54CLT1G</t>
   </si>
   <si>
     <t>SOT-23</t>
   </si>
   <si>
-    <t>D3</t>
-  </si>
-  <si>
-    <t>D_Schottky</t>
-  </si>
-  <si>
-    <t>D_SMA</t>
-  </si>
-  <si>
     <t>FB1</t>
   </si>
   <si>
@@ -172,6 +211,24 @@
     <t>L_0603_1608Metric</t>
   </si>
   <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>Conn_02x03_Odd_Even</t>
+  </si>
+  <si>
+    <t>Molex_Mini-Fit_Jr_5566-06A_2x03_P4.20mm_Vertical</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>Conn_02x02_Counter_Clockwise</t>
+  </si>
+  <si>
+    <t>Molex_Mini-Fit_Jr_5566-04A_2x02_P4.20mm_Vertical</t>
+  </si>
+  <si>
     <t>J3</t>
   </si>
   <si>
@@ -184,96 +241,114 @@
     <t>L1</t>
   </si>
   <si>
-    <t>10ÂµH</t>
-  </si>
-  <si>
-    <t>L_Sunlord_MWSA1204S-100</t>
+    <t>2.2ÂµH</t>
+  </si>
+  <si>
+    <t>IND-SMD_L7.0-W6.6</t>
   </si>
   <si>
     <t>Q1</t>
   </si>
   <si>
+    <t>AO4407A</t>
+  </si>
+  <si>
+    <t>SOIC127P600X175-8N</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
     <t>MMBT3904</t>
   </si>
   <si>
+    <t>TSOT-23</t>
+  </si>
+  <si>
     <t>R1</t>
   </si>
   <si>
-    <t>200kÎ©</t>
-  </si>
-  <si>
-    <t>R_0402_1005Metric</t>
+    <t>23.7kÎ©</t>
+  </si>
+  <si>
+    <t>R_0603_1608Metric</t>
   </si>
   <si>
     <t>R2</t>
   </si>
   <si>
-    <t>52.3kÎ©</t>
+    <t>80.6kÎ©</t>
   </si>
   <si>
     <t>R3</t>
   </si>
   <si>
+    <t>60.4kÎ©</t>
+  </si>
+  <si>
+    <t>R4</t>
+  </si>
+  <si>
+    <t>11.5kÎ©</t>
+  </si>
+  <si>
+    <t>R5</t>
+  </si>
+  <si>
+    <t>84.5kÎ©</t>
+  </si>
+  <si>
+    <t>R6</t>
+  </si>
+  <si>
+    <t>22kÎ©</t>
+  </si>
+  <si>
+    <t>R7</t>
+  </si>
+  <si>
+    <t>1kÎ©</t>
+  </si>
+  <si>
+    <t>R8</t>
+  </si>
+  <si>
+    <t>47kÎ©</t>
+  </si>
+  <si>
+    <t>R9</t>
+  </si>
+  <si>
     <t>10kÎ©</t>
   </si>
   <si>
-    <t>R4</t>
-  </si>
-  <si>
-    <t>15kÎ©</t>
-  </si>
-  <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>22kÎ©</t>
-  </si>
-  <si>
-    <t>R7</t>
-  </si>
-  <si>
-    <t>R8</t>
+    <t>R10</t>
   </si>
   <si>
     <t>100kÎ©</t>
   </si>
   <si>
-    <t>R9</t>
-  </si>
-  <si>
-    <t>84.5kÎ©</t>
-  </si>
-  <si>
-    <t>R10</t>
-  </si>
-  <si>
     <t>R11</t>
   </si>
   <si>
-    <t>1kÎ©</t>
+    <t>4.7kÎ©</t>
   </si>
   <si>
     <t>R12</t>
   </si>
   <si>
-    <t>47kÎ©</t>
-  </si>
-  <si>
     <t>R13</t>
   </si>
   <si>
+    <t>470Î©</t>
+  </si>
+  <si>
     <t>R14</t>
   </si>
   <si>
     <t>R15</t>
   </si>
   <si>
-    <t>470Î©</t>
-  </si>
-  <si>
     <t>R16</t>
   </si>
   <si>
@@ -292,9 +367,6 @@
     <t>R21</t>
   </si>
   <si>
-    <t>4.7kÎ©</t>
-  </si>
-  <si>
     <t>R22</t>
   </si>
   <si>
@@ -310,34 +382,34 @@
     <t>R26</t>
   </si>
   <si>
-    <t>R27</t>
-  </si>
-  <si>
-    <t>R28</t>
+    <t>REF**</t>
+  </si>
+  <si>
+    <t>RPI_Hat_B+</t>
   </si>
   <si>
     <t>U1</t>
   </si>
   <si>
+    <t>TPS54560BQDDARQ1</t>
+  </si>
+  <si>
+    <t>Texas_R-PDSO-G8_EP2.95x4.9mm_Mask2.4x3.1mm_ThermalVias</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>TL431DBZ</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
     <t>PCM5122PWR</t>
   </si>
   <si>
-    <t>SOP65P640X120-28N</t>
-  </si>
-  <si>
-    <t>U2</t>
-  </si>
-  <si>
-    <t>TPS54560BQDDARQ1</t>
-  </si>
-  <si>
-    <t>Texas_R-PDSO-G8_EP2.95x4.9mm_Mask2.4x3.1mm_ThermalVias</t>
-  </si>
-  <si>
-    <t>U3</t>
-  </si>
-  <si>
-    <t>TL431DBZ</t>
+    <t>TSSOP-28_4.4x9.7mm_P0.65mm</t>
   </si>
   <si>
     <t>U4</t>
@@ -352,28 +424,25 @@
     <t>U5</t>
   </si>
   <si>
-    <t>Optocoupler_DC_PhotoNPN_AKEC</t>
-  </si>
-  <si>
-    <t>SOIC254P1016X385-4N</t>
+    <t>ADS1115IDGSR</t>
+  </si>
+  <si>
+    <t>SOP50P490X110-10N</t>
   </si>
   <si>
     <t>U6</t>
   </si>
   <si>
-    <t>U7</t>
-  </si>
-  <si>
-    <t>U8</t>
-  </si>
-  <si>
-    <t>U9</t>
-  </si>
-  <si>
-    <t>ADS1115IDGS</t>
-  </si>
-  <si>
-    <t>IC_ADS1115IRUGR</t>
+    <t>LTV-847S</t>
+  </si>
+  <si>
+    <t>SMDIP-16_W9.53mm</t>
+  </si>
+  <si>
+    <t>Designator</t>
+  </si>
+  <si>
+    <t>Value</t>
   </si>
   <si>
     <t>Mid X</t>
@@ -386,12 +455,6 @@
   </si>
   <si>
     <t>Layer</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>Designator</t>
   </si>
 </sst>
 </file>
@@ -1251,31 +1314,31 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{789D5727-76C8-46F3-9214-DEA4DF325AB5}">
-  <dimension ref="A1:G70"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AA95EEF-724F-429A-8A74-C19C395512E3}">
+  <dimension ref="A1:G78"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
       <c r="B1" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C1" t="s">
         <v>0</v>
       </c>
       <c r="D1" t="s">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="E1" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="F1" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="G1" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -1289,10 +1352,10 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>131.85468700000001</v>
+        <v>80.924259000000006</v>
       </c>
       <c r="E2">
-        <v>-57.443264999999997</v>
+        <v>-37.865170999999997</v>
       </c>
       <c r="F2">
         <v>-90</v>
@@ -1312,591 +1375,591 @@
         <v>7</v>
       </c>
       <c r="D3">
-        <v>135.905</v>
+        <v>131</v>
       </c>
       <c r="E3">
-        <v>-47.338453000000001</v>
+        <v>-56.756684</v>
       </c>
       <c r="F3">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C4" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D4">
-        <v>111.53</v>
+        <v>128.44999999999999</v>
       </c>
       <c r="E4">
-        <v>-48.098556000000002</v>
+        <v>-54.45</v>
       </c>
       <c r="F4">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G4" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" t="s">
         <v>11</v>
       </c>
-      <c r="C5" t="s">
-        <v>12</v>
-      </c>
       <c r="D5">
-        <v>107.391094</v>
+        <v>135</v>
       </c>
       <c r="E5">
-        <v>-52.046117000000002</v>
+        <v>-45</v>
       </c>
       <c r="F5">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G5" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D6">
-        <v>132.350312</v>
+        <v>132</v>
       </c>
       <c r="E6">
-        <v>-45.818247</v>
+        <v>-45</v>
       </c>
       <c r="F6">
         <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="s">
         <v>7</v>
       </c>
       <c r="D7">
-        <v>128.287812</v>
+        <v>121.02500000000001</v>
       </c>
       <c r="E7">
-        <v>-45.058143999999999</v>
+        <v>-52.207954999999998</v>
       </c>
       <c r="F7">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="G7" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" t="s">
         <v>17</v>
       </c>
-      <c r="B8" t="s">
-        <v>2</v>
-      </c>
       <c r="C8" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D8">
-        <v>108.7075</v>
+        <v>121.017313</v>
       </c>
       <c r="E8">
-        <v>-61.203676999999999</v>
+        <v>-54.5</v>
       </c>
       <c r="F8">
         <v>0</v>
       </c>
       <c r="G8" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C9" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D9">
-        <v>126.227031</v>
+        <v>113.5</v>
       </c>
       <c r="E9">
-        <v>-85.526978</v>
+        <v>-47.5</v>
       </c>
       <c r="F9">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G9" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D10">
-        <v>126.452656</v>
+        <v>127.91014</v>
       </c>
       <c r="E10">
-        <v>-68.564605</v>
+        <v>-64.506120999999993</v>
       </c>
       <c r="F10">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G10" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D11">
-        <v>129</v>
+        <v>81.357922000000002</v>
       </c>
       <c r="E11">
-        <v>-70.45</v>
+        <v>-46.251710000000003</v>
       </c>
       <c r="F11">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G11" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C12" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D12">
-        <v>101.062031</v>
+        <v>81.427916999999994</v>
       </c>
       <c r="E12">
-        <v>-55.389484000000003</v>
+        <v>-53.713329000000002</v>
       </c>
       <c r="F12">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G12" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D13">
-        <v>98.761388999999994</v>
+        <v>81.405199999999994</v>
       </c>
       <c r="E13">
-        <v>-56.993153</v>
+        <v>-52.127403999999999</v>
       </c>
       <c r="F13">
         <v>0</v>
       </c>
       <c r="G13" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="B14" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D14">
-        <v>95.983906000000005</v>
+        <v>86.060128000000006</v>
       </c>
       <c r="E14">
-        <v>-56.656323</v>
+        <v>-71.210543000000001</v>
       </c>
       <c r="F14">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G14" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="B15" t="s">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D15">
-        <v>96.52</v>
+        <v>87.560128000000006</v>
       </c>
       <c r="E15">
-        <v>-59.176735999999998</v>
+        <v>-71.210543000000001</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G15" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="C16" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D16">
-        <v>120.02</v>
+        <v>86</v>
       </c>
       <c r="E16">
-        <v>-70</v>
+        <v>-59.008097999999997</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="D17">
-        <v>94.784374999999997</v>
+        <v>87.510487999999995</v>
       </c>
       <c r="E17">
-        <v>-44.014775999999998</v>
+        <v>-58.994264999999999</v>
       </c>
       <c r="F17">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G17" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D18">
-        <v>99.538594000000003</v>
+        <v>82.5</v>
       </c>
       <c r="E18">
-        <v>-45.254776</v>
+        <v>-59</v>
       </c>
       <c r="F18">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G18" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
+        <v>33</v>
+      </c>
+      <c r="B19" t="s">
         <v>28</v>
       </c>
-      <c r="B19" t="s">
-        <v>29</v>
-      </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D19">
-        <v>82.522439000000006</v>
+        <v>91.405750999999995</v>
       </c>
       <c r="E19">
-        <v>-51.720599</v>
+        <v>-67.964652999999998</v>
       </c>
       <c r="F19">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G19" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B20" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="D20">
-        <v>82.420080999999996</v>
+        <v>91.405750999999995</v>
       </c>
       <c r="E20">
-        <v>-53.463957999999998</v>
+        <v>-66.464652999999998</v>
       </c>
       <c r="F20">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G20" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B21" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C21" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D21">
-        <v>95.983906000000005</v>
+        <v>91.390635000000003</v>
       </c>
       <c r="E21">
-        <v>-55.136116999999999</v>
+        <v>-63.575454000000001</v>
       </c>
       <c r="F21">
         <v>0</v>
       </c>
       <c r="G21" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B22" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D22">
-        <v>97.5</v>
+        <v>91.385880999999998</v>
       </c>
       <c r="E22">
-        <v>-67.02</v>
+        <v>-62.043990000000001</v>
       </c>
       <c r="F22">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G22" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B23" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>110.260469</v>
+        <v>90.517555999999999</v>
       </c>
       <c r="E23">
-        <v>-66.341031000000001</v>
+        <v>-59</v>
       </c>
       <c r="F23">
         <v>90</v>
       </c>
       <c r="G23" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B24" t="s">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="C24" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D24">
-        <v>88.366718000000006</v>
+        <v>89.017555999999999</v>
       </c>
       <c r="E24">
-        <v>-70.591547000000006</v>
+        <v>-59</v>
       </c>
       <c r="F24">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G24" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B25" t="s">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D25">
-        <v>127.02</v>
+        <v>84.554844000000003</v>
       </c>
       <c r="E25">
-        <v>-72</v>
+        <v>-71.232516000000004</v>
       </c>
       <c r="F25">
-        <v>180</v>
+        <v>-90</v>
       </c>
       <c r="G25" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" t="s">
-        <v>6</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="D26">
-        <v>125</v>
+        <v>80.033381000000006</v>
       </c>
       <c r="E26">
-        <v>-81.5</v>
+        <v>-71.232516000000004</v>
       </c>
       <c r="F26">
         <v>90</v>
       </c>
       <c r="G26" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C27" t="s">
-        <v>40</v>
+        <v>11</v>
       </c>
       <c r="D27">
-        <v>126.26921900000001</v>
+        <v>94.306578000000002</v>
       </c>
       <c r="E27">
-        <v>-63.854399000000001</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F27">
         <v>-90</v>
       </c>
       <c r="G27" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="C28" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D28">
-        <v>108.9375</v>
+        <v>99.037718999999996</v>
       </c>
       <c r="E28">
-        <v>-57.95</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F28">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G28" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1904,367 +1967,367 @@
         <v>44</v>
       </c>
       <c r="B29" t="s">
-        <v>45</v>
+        <v>10</v>
       </c>
       <c r="C29" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
       <c r="D29">
-        <v>132.91517400000001</v>
+        <v>103.76885900000001</v>
       </c>
       <c r="E29">
-        <v>-42.191201999999997</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G29" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B30" t="s">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="C30" t="s">
-        <v>49</v>
+        <v>11</v>
       </c>
       <c r="D30">
-        <v>120.178906</v>
+        <v>108.5</v>
       </c>
       <c r="E30">
-        <v>-73.625431000000006</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F30">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G30" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>11</v>
       </c>
       <c r="D31">
-        <v>81.026955999999998</v>
+        <v>92.470519999999993</v>
       </c>
       <c r="E31">
-        <v>-45.240487000000002</v>
+        <v>-71.493786999999998</v>
       </c>
       <c r="F31">
         <v>0</v>
       </c>
       <c r="G31" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>10</v>
       </c>
       <c r="C32" t="s">
-        <v>55</v>
+        <v>11</v>
       </c>
       <c r="D32">
-        <v>120.09343699999999</v>
+        <v>92.470519999999993</v>
       </c>
       <c r="E32">
-        <v>-50.973058000000002</v>
+        <v>-72.98</v>
       </c>
       <c r="F32">
         <v>180</v>
       </c>
       <c r="G32" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="B33" t="s">
-        <v>57</v>
+        <v>10</v>
       </c>
       <c r="C33" t="s">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="D33">
-        <v>127.4375</v>
+        <v>102.47051999999999</v>
       </c>
       <c r="E33">
-        <v>-76.5625</v>
+        <v>-72.989191000000005</v>
       </c>
       <c r="F33">
-        <v>-90</v>
+        <v>0</v>
       </c>
       <c r="G33" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B34" t="s">
-        <v>59</v>
+        <v>10</v>
       </c>
       <c r="C34" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D34">
-        <v>134.34375</v>
+        <v>102.47051999999999</v>
       </c>
       <c r="E34">
-        <v>-55.632852</v>
+        <v>-71.484595999999996</v>
       </c>
       <c r="F34">
         <v>0</v>
       </c>
       <c r="G34" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B35" t="s">
-        <v>62</v>
+        <v>10</v>
       </c>
       <c r="C35" t="s">
-        <v>60</v>
+        <v>11</v>
       </c>
       <c r="D35">
-        <v>135.91499999999999</v>
+        <v>102.47051999999999</v>
       </c>
       <c r="E35">
-        <v>-49.598762000000001</v>
+        <v>-68.493786999999998</v>
       </c>
       <c r="F35">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G35" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B36" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C36" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D36">
-        <v>128.55171899999999</v>
+        <v>122.6</v>
       </c>
       <c r="E36">
-        <v>-47.318452999999998</v>
+        <v>-59.141679000000003</v>
       </c>
       <c r="F36">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G36" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="C37" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D37">
-        <v>130.07515599999999</v>
+        <v>127</v>
       </c>
       <c r="E37">
-        <v>-45.798247000000003</v>
+        <v>-47.57</v>
       </c>
       <c r="F37">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G37" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B38" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D38">
-        <v>91.6875</v>
+        <v>125.0625</v>
       </c>
       <c r="E38">
-        <v>-69.061340999999999</v>
+        <v>-64.55</v>
       </c>
       <c r="F38">
         <v>180</v>
       </c>
       <c r="G38" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="B39" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="C39" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D39">
-        <v>111.746094</v>
+        <v>81.366398000000004</v>
       </c>
       <c r="E39">
-        <v>-61.206941999999998</v>
+        <v>-44.626080999999999</v>
       </c>
       <c r="F39">
         <v>0</v>
       </c>
       <c r="G39" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="B40" t="s">
         <v>64</v>
       </c>
       <c r="C40" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="D40">
-        <v>85.641561999999993</v>
+        <v>133.5</v>
       </c>
       <c r="E40">
-        <v>-64.547456999999994</v>
+        <v>-71.5</v>
       </c>
       <c r="F40">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G40" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="B41" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C41" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="D41">
-        <v>111.746094</v>
+        <v>99.6</v>
       </c>
       <c r="E41">
-        <v>-59.686736000000003</v>
+        <v>-85.5</v>
       </c>
       <c r="F41">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G41" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B42" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C42" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="D42">
-        <v>127.488281</v>
+        <v>82</v>
       </c>
       <c r="E42">
-        <v>-87.557184000000007</v>
+        <v>-78.5</v>
       </c>
       <c r="F42">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="G42" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B43" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="C43" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="D43">
-        <v>125.203125</v>
+        <v>119.5</v>
       </c>
       <c r="E43">
-        <v>-87.557184000000007</v>
+        <v>-47.5</v>
       </c>
       <c r="F43">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G43" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
+        <v>75</v>
+      </c>
+      <c r="B44" t="s">
         <v>76</v>
       </c>
-      <c r="B44" t="s">
+      <c r="C44" t="s">
         <v>77</v>
       </c>
-      <c r="C44" t="s">
-        <v>60</v>
-      </c>
       <c r="D44">
-        <v>129.773437</v>
+        <v>131.517293</v>
       </c>
       <c r="E44">
-        <v>-81.222990999999993</v>
+        <v>-62.267769000000001</v>
       </c>
       <c r="F44">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G44" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.35">
@@ -2275,594 +2338,778 @@
         <v>79</v>
       </c>
       <c r="C45" t="s">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="D45">
-        <v>124.89194999999999</v>
+        <v>115.918674</v>
       </c>
       <c r="E45">
-        <v>-79.265769000000006</v>
+        <v>-57.995362</v>
       </c>
       <c r="F45">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G45" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D46">
-        <v>128</v>
+        <v>133.5</v>
       </c>
       <c r="E46">
-        <v>-79.989999999999995</v>
+        <v>-45</v>
       </c>
       <c r="F46">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G46" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B47" t="s">
-        <v>64</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D47">
-        <v>91.227500000000006</v>
+        <v>135.17500000000001</v>
       </c>
       <c r="E47">
-        <v>-58.466631999999997</v>
+        <v>-57</v>
       </c>
       <c r="F47">
-        <v>90</v>
+        <v>-90</v>
       </c>
       <c r="G47" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="B48" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" t="s">
         <v>83</v>
       </c>
-      <c r="C48" t="s">
-        <v>60</v>
-      </c>
       <c r="D48">
-        <v>82.693988000000004</v>
+        <v>123.5</v>
       </c>
       <c r="E48">
-        <v>-54.974164000000002</v>
+        <v>-41.5</v>
       </c>
       <c r="F48">
         <v>180</v>
       </c>
       <c r="G48" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="B49" t="s">
+        <v>89</v>
+      </c>
+      <c r="C49" t="s">
         <v>83</v>
       </c>
-      <c r="C49" t="s">
-        <v>60</v>
-      </c>
       <c r="D49">
-        <v>85.026955999999998</v>
+        <v>123.5</v>
       </c>
       <c r="E49">
-        <v>-51.980486999999997</v>
+        <v>-43</v>
       </c>
       <c r="F49">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G49" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B50" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
       <c r="C50" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D50">
-        <v>91.941406000000001</v>
+        <v>112.69480299999999</v>
       </c>
       <c r="E50">
-        <v>-55.126117000000001</v>
+        <v>-55.184556000000001</v>
       </c>
       <c r="F50">
         <v>0</v>
       </c>
       <c r="G50" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C51" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D51">
-        <v>89.148437000000001</v>
+        <v>112.675</v>
       </c>
       <c r="E51">
-        <v>-55.126117000000001</v>
+        <v>-53.69</v>
       </c>
       <c r="F51">
         <v>0</v>
       </c>
       <c r="G51" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="B52" t="s">
-        <v>64</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D52">
-        <v>125</v>
+        <v>112.687273</v>
       </c>
       <c r="E52">
-        <v>-83.51</v>
+        <v>-50.652211999999999</v>
       </c>
       <c r="F52">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G52" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="B53" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="C53" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D53">
-        <v>115.5</v>
+        <v>112.687273</v>
       </c>
       <c r="E53">
-        <v>-70.989999999999995</v>
+        <v>-52.153984000000001</v>
       </c>
       <c r="F53">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G53" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="B54" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="C54" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D54">
-        <v>105.95406199999999</v>
+        <v>112.68398999999999</v>
       </c>
       <c r="E54">
-        <v>-57.199793999999997</v>
+        <v>-56.701093</v>
       </c>
       <c r="F54">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G54" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="B55" t="s">
-        <v>64</v>
+        <v>101</v>
       </c>
       <c r="C55" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D55">
-        <v>99.01</v>
+        <v>125</v>
       </c>
       <c r="E55">
-        <v>-68.554604999999995</v>
+        <v>-67</v>
       </c>
       <c r="F55">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="G55" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>102</v>
       </c>
       <c r="B56" t="s">
-        <v>64</v>
+        <v>103</v>
       </c>
       <c r="C56" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D56">
-        <v>90.671875</v>
+        <v>128</v>
       </c>
       <c r="E56">
-        <v>-72.101753000000002</v>
+        <v>-67</v>
       </c>
       <c r="F56">
         <v>180</v>
       </c>
       <c r="G56" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
+        <v>104</v>
+      </c>
+      <c r="B57" t="s">
         <v>93</v>
       </c>
-      <c r="B57" t="s">
-        <v>64</v>
-      </c>
       <c r="C57" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D57">
-        <v>109.714844</v>
+        <v>122.200374</v>
       </c>
       <c r="E57">
-        <v>-69.314708999999993</v>
+        <v>-66.285730999999998</v>
       </c>
       <c r="F57">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G57" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B58" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C58" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D58">
-        <v>85.641561999999993</v>
+        <v>83.047690000000003</v>
       </c>
       <c r="E58">
-        <v>-68.854709</v>
+        <v>-71.232516000000004</v>
       </c>
       <c r="F58">
         <v>90</v>
       </c>
       <c r="G58" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>107</v>
       </c>
       <c r="B59" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="C59" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D59">
-        <v>91.6875</v>
+        <v>81.540535000000006</v>
       </c>
       <c r="E59">
-        <v>-65.007457000000002</v>
+        <v>-71.232516000000004</v>
       </c>
       <c r="F59">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="G59" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="B60" t="s">
+        <v>99</v>
+      </c>
+      <c r="C60" t="s">
+        <v>83</v>
+      </c>
+      <c r="D60">
+        <v>91.941007999999997</v>
+      </c>
+      <c r="E60">
+        <v>-55.961047999999998</v>
+      </c>
+      <c r="F60">
         <v>90</v>
       </c>
-      <c r="C60" t="s">
-        <v>60</v>
-      </c>
-      <c r="D60">
-        <v>88.386718999999999</v>
-      </c>
-      <c r="E60">
-        <v>-72.101753000000002</v>
-      </c>
-      <c r="F60">
-        <v>0</v>
-      </c>
       <c r="G60" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="B61" t="s">
+        <v>99</v>
+      </c>
+      <c r="C61" t="s">
+        <v>83</v>
+      </c>
+      <c r="D61">
+        <v>96.672149000000005</v>
+      </c>
+      <c r="E61">
+        <v>-55.961047999999998</v>
+      </c>
+      <c r="F61">
         <v>90</v>
       </c>
-      <c r="C61" t="s">
-        <v>60</v>
-      </c>
-      <c r="D61">
-        <v>86.101562000000001</v>
-      </c>
-      <c r="E61">
-        <v>-70.834914999999995</v>
-      </c>
-      <c r="F61">
-        <v>0</v>
-      </c>
       <c r="G61" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>110</v>
       </c>
       <c r="B62" t="s">
         <v>99</v>
       </c>
       <c r="C62" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="D62">
-        <v>93.318437000000003</v>
+        <v>101.403289</v>
       </c>
       <c r="E62">
-        <v>-50.170959000000003</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F62">
-        <v>-90</v>
+        <v>90</v>
       </c>
       <c r="G62" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B63" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
-        <v>103</v>
+        <v>83</v>
       </c>
       <c r="D63">
-        <v>132.15125</v>
+        <v>106.13442999999999</v>
       </c>
       <c r="E63">
-        <v>-50.882646000000001</v>
+        <v>-55.961047999999998</v>
       </c>
       <c r="F63">
         <v>90</v>
       </c>
       <c r="G63" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B64" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C64" t="s">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="D64">
-        <v>129.9375</v>
+        <v>98.35</v>
       </c>
       <c r="E64">
-        <v>-83.45</v>
+        <v>-74.5</v>
       </c>
       <c r="F64">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="G64" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B65" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="D65">
-        <v>123.6375</v>
+        <v>96.84</v>
       </c>
       <c r="E65">
-        <v>-70.95</v>
+        <v>-74.5</v>
       </c>
       <c r="F65">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G65" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="B66" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C66" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D66">
-        <v>121.77</v>
+        <v>99.86</v>
       </c>
       <c r="E66">
-        <v>-81.459999999999994</v>
+        <v>-74.5</v>
       </c>
       <c r="F66">
         <v>90</v>
       </c>
       <c r="G66" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="B67" t="s">
-        <v>110</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D67">
-        <v>117.21618700000001</v>
+        <v>95.33</v>
       </c>
       <c r="E67">
-        <v>-64.889155000000002</v>
+        <v>-74.5</v>
       </c>
       <c r="F67">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G67" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="B68" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C68" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D68">
-        <v>102.77</v>
+        <v>92.470519999999993</v>
       </c>
       <c r="E68">
-        <v>-64.540000000000006</v>
+        <v>-69.98</v>
       </c>
       <c r="F68">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="G68" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B69" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="C69" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="D69">
-        <v>111.73</v>
+        <v>92.470519999999993</v>
       </c>
       <c r="E69">
-        <v>-80.349999999999994</v>
+        <v>-74.48</v>
       </c>
       <c r="F69">
-        <v>-90</v>
+        <v>180</v>
       </c>
       <c r="G69" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="B70" t="s">
-        <v>116</v>
+        <v>99</v>
       </c>
       <c r="C70" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="D70">
-        <v>88.64</v>
+        <v>102.47051999999999</v>
       </c>
       <c r="E70">
-        <v>-66</v>
+        <v>-74.493786999999998</v>
       </c>
       <c r="F70">
+        <v>0</v>
+      </c>
+      <c r="G70" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A71" t="s">
+        <v>119</v>
+      </c>
+      <c r="B71" t="s">
+        <v>99</v>
+      </c>
+      <c r="C71" t="s">
+        <v>83</v>
+      </c>
+      <c r="D71">
+        <v>102.47051999999999</v>
+      </c>
+      <c r="E71">
+        <v>-69.98</v>
+      </c>
+      <c r="F71">
+        <v>0</v>
+      </c>
+      <c r="G71" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A72" t="s">
+        <v>120</v>
+      </c>
+      <c r="B72" t="s">
+        <v>121</v>
+      </c>
+      <c r="C72" t="s">
+        <v>121</v>
+      </c>
+      <c r="D72">
+        <v>105.026956</v>
+      </c>
+      <c r="E72">
+        <v>-36.490487000000002</v>
+      </c>
+      <c r="F72">
+        <v>0</v>
+      </c>
+      <c r="G72" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" t="s">
+        <v>122</v>
+      </c>
+      <c r="B73" t="s">
+        <v>123</v>
+      </c>
+      <c r="C73" t="s">
+        <v>124</v>
+      </c>
+      <c r="D73">
+        <v>133.47</v>
+      </c>
+      <c r="E73">
+        <v>-51.6</v>
+      </c>
+      <c r="F73">
+        <v>90</v>
+      </c>
+      <c r="G73" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74" t="s">
+        <v>125</v>
+      </c>
+      <c r="B74" t="s">
+        <v>126</v>
+      </c>
+      <c r="C74" t="s">
+        <v>59</v>
+      </c>
+      <c r="D74">
+        <v>116.254795</v>
+      </c>
+      <c r="E74">
+        <v>-53</v>
+      </c>
+      <c r="F74">
+        <v>0</v>
+      </c>
+      <c r="G74" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A75" t="s">
+        <v>127</v>
+      </c>
+      <c r="B75" t="s">
+        <v>128</v>
+      </c>
+      <c r="C75" t="s">
+        <v>129</v>
+      </c>
+      <c r="D75">
+        <v>84.048593999999994</v>
+      </c>
+      <c r="E75">
+        <v>-65.002291999999997</v>
+      </c>
+      <c r="F75">
         <v>-90</v>
       </c>
-      <c r="G70" t="s">
-        <v>4</v>
+      <c r="G75" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A76" t="s">
+        <v>130</v>
+      </c>
+      <c r="B76" t="s">
+        <v>131</v>
+      </c>
+      <c r="C76" t="s">
+        <v>132</v>
+      </c>
+      <c r="D76">
+        <v>81.317499999999995</v>
+      </c>
+      <c r="E76">
+        <v>-49.158360999999999</v>
+      </c>
+      <c r="F76">
+        <v>-90</v>
+      </c>
+      <c r="G76" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A77" t="s">
+        <v>133</v>
+      </c>
+      <c r="B77" t="s">
+        <v>134</v>
+      </c>
+      <c r="C77" t="s">
+        <v>135</v>
+      </c>
+      <c r="D77">
+        <v>97.35</v>
+      </c>
+      <c r="E77">
+        <v>-71</v>
+      </c>
+      <c r="F77">
+        <v>0</v>
+      </c>
+      <c r="G77" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A78" t="s">
+        <v>136</v>
+      </c>
+      <c r="B78" t="s">
+        <v>137</v>
+      </c>
+      <c r="C78" t="s">
+        <v>138</v>
+      </c>
+      <c r="D78">
+        <v>100.478258</v>
+      </c>
+      <c r="E78">
+        <v>-48.381616999999999</v>
+      </c>
+      <c r="F78">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
